--- a/data/MK_ECB_DATA_20260610.xlsx
+++ b/data/MK_ECB_DATA_20260610.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E268"/>
+  <dimension ref="A1:E274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3608,25 +3608,25 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_1Y</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>유로존 국채금리 2년</t>
+          <t>유로존 국채금리 1년</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2.709578</v>
+        <v>2.599927</v>
       </c>
     </row>
     <row r="140">
@@ -3645,11 +3645,11 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2.713377</v>
+        <v>2.709578</v>
       </c>
     </row>
     <row r="141">
@@ -3668,11 +3668,11 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2.580816</v>
+        <v>2.713377</v>
       </c>
     </row>
     <row r="142">
@@ -3691,11 +3691,11 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2.563197</v>
+        <v>2.580816</v>
       </c>
     </row>
     <row r="143">
@@ -3714,11 +3714,11 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2.590769</v>
+        <v>2.563197</v>
       </c>
     </row>
     <row r="144">
@@ -3737,11 +3737,11 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2.651872</v>
+        <v>2.590769</v>
       </c>
     </row>
     <row r="145">
@@ -3760,11 +3760,11 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2.734067</v>
+        <v>2.651872</v>
       </c>
     </row>
     <row r="146">
@@ -3783,11 +3783,11 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2.720401</v>
+        <v>2.734067</v>
       </c>
     </row>
     <row r="147">
@@ -3806,11 +3806,11 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>2.673633</v>
+        <v>2.720401</v>
       </c>
     </row>
     <row r="148">
@@ -3829,11 +3829,11 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>2.759799</v>
+        <v>2.673633</v>
       </c>
     </row>
     <row r="149">
@@ -3852,11 +3852,11 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2.701019</v>
+        <v>2.759799</v>
       </c>
     </row>
     <row r="150">
@@ -3875,11 +3875,11 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2.758581</v>
+        <v>2.701019</v>
       </c>
     </row>
     <row r="151">
@@ -3898,11 +3898,11 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2.732917</v>
+        <v>2.758581</v>
       </c>
     </row>
     <row r="152">
@@ -3921,11 +3921,11 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2.690643</v>
+        <v>2.732917</v>
       </c>
     </row>
     <row r="153">
@@ -3944,11 +3944,11 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2.649058</v>
+        <v>2.690643</v>
       </c>
     </row>
     <row r="154">
@@ -3967,11 +3967,11 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2.550151</v>
+        <v>2.649058</v>
       </c>
     </row>
     <row r="155">
@@ -3990,11 +3990,11 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2.600158</v>
+        <v>2.550151</v>
       </c>
     </row>
     <row r="156">
@@ -4013,11 +4013,11 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>2.584193</v>
+        <v>2.600158</v>
       </c>
     </row>
     <row r="157">
@@ -4036,11 +4036,11 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2.60767</v>
+        <v>2.584193</v>
       </c>
     </row>
     <row r="158">
@@ -4059,11 +4059,11 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2.573921</v>
+        <v>2.60767</v>
       </c>
     </row>
     <row r="159">
@@ -4082,11 +4082,11 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2.664843</v>
+        <v>2.573921</v>
       </c>
     </row>
     <row r="160">
@@ -4105,11 +4105,11 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>2.631211</v>
+        <v>2.664843</v>
       </c>
     </row>
     <row r="161">
@@ -4128,11 +4128,11 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2.668913</v>
+        <v>2.631211</v>
       </c>
     </row>
     <row r="162">
@@ -4151,11 +4151,11 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>2.667137</v>
+        <v>2.668913</v>
       </c>
     </row>
     <row r="163">
@@ -4174,11 +4174,11 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>2.690449</v>
+        <v>2.667137</v>
       </c>
     </row>
     <row r="164">
@@ -4197,57 +4197,57 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2.70087</v>
+        <v>2.690449</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>유로존 국채금리 3년</t>
+          <t>유로존 국채금리 2년</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>2.785695</v>
+        <v>2.70087</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>유로존 국채금리 3년</t>
+          <t>유로존 국채금리 2년</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>2.791931</v>
+        <v>2.687806</v>
       </c>
     </row>
     <row r="167">
@@ -4266,11 +4266,11 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>2.660543</v>
+        <v>2.785695</v>
       </c>
     </row>
     <row r="168">
@@ -4289,11 +4289,11 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>2.647172</v>
+        <v>2.791931</v>
       </c>
     </row>
     <row r="169">
@@ -4312,11 +4312,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>2.668906</v>
+        <v>2.660543</v>
       </c>
     </row>
     <row r="170">
@@ -4335,11 +4335,11 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>2.727433</v>
+        <v>2.647172</v>
       </c>
     </row>
     <row r="171">
@@ -4358,11 +4358,11 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>2.812236</v>
+        <v>2.668906</v>
       </c>
     </row>
     <row r="172">
@@ -4381,11 +4381,11 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2.800452</v>
+        <v>2.727433</v>
       </c>
     </row>
     <row r="173">
@@ -4404,11 +4404,11 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2.746714</v>
+        <v>2.812236</v>
       </c>
     </row>
     <row r="174">
@@ -4427,11 +4427,11 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>2.846863</v>
+        <v>2.800452</v>
       </c>
     </row>
     <row r="175">
@@ -4450,11 +4450,11 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>2.787952</v>
+        <v>2.746714</v>
       </c>
     </row>
     <row r="176">
@@ -4473,11 +4473,11 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>2.854181</v>
+        <v>2.846863</v>
       </c>
     </row>
     <row r="177">
@@ -4496,11 +4496,11 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>2.823594</v>
+        <v>2.787952</v>
       </c>
     </row>
     <row r="178">
@@ -4519,11 +4519,11 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>2.775414</v>
+        <v>2.854181</v>
       </c>
     </row>
     <row r="179">
@@ -4542,11 +4542,11 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>2.73301</v>
+        <v>2.823594</v>
       </c>
     </row>
     <row r="180">
@@ -4565,11 +4565,11 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>2.632702</v>
+        <v>2.775414</v>
       </c>
     </row>
     <row r="181">
@@ -4588,11 +4588,11 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>2.685019</v>
+        <v>2.73301</v>
       </c>
     </row>
     <row r="182">
@@ -4611,11 +4611,11 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>2.665718</v>
+        <v>2.632702</v>
       </c>
     </row>
     <row r="183">
@@ -4634,11 +4634,11 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>2.685927</v>
+        <v>2.685019</v>
       </c>
     </row>
     <row r="184">
@@ -4657,11 +4657,11 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>2.653732</v>
+        <v>2.665718</v>
       </c>
     </row>
     <row r="185">
@@ -4680,11 +4680,11 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>2.737626</v>
+        <v>2.685927</v>
       </c>
     </row>
     <row r="186">
@@ -4703,11 +4703,11 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>2.695968</v>
+        <v>2.653732</v>
       </c>
     </row>
     <row r="187">
@@ -4726,11 +4726,11 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>2.739566</v>
+        <v>2.737626</v>
       </c>
     </row>
     <row r="188">
@@ -4749,11 +4749,11 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2.742955</v>
+        <v>2.695968</v>
       </c>
     </row>
     <row r="189">
@@ -4772,11 +4772,11 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>2.76777</v>
+        <v>2.739566</v>
       </c>
     </row>
     <row r="190">
@@ -4795,80 +4795,80 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>2.775779</v>
+        <v>2.742955</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>유로존 국채금리 5년</t>
+          <t>유로존 국채금리 3년</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>3.000517</v>
+        <v>2.76777</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>유로존 국채금리 5년</t>
+          <t>유로존 국채금리 3년</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>3.007991</v>
+        <v>2.775779</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>유로존 국채금리 5년</t>
+          <t>유로존 국채금리 3년</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>2.886073</v>
+        <v>2.765536</v>
       </c>
     </row>
     <row r="194">
@@ -4887,11 +4887,11 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>2.876206</v>
+        <v>3.000517</v>
       </c>
     </row>
     <row r="195">
@@ -4910,11 +4910,11 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>2.889313</v>
+        <v>3.007991</v>
       </c>
     </row>
     <row r="196">
@@ -4933,11 +4933,11 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>2.939157</v>
+        <v>2.886073</v>
       </c>
     </row>
     <row r="197">
@@ -4956,11 +4956,11 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>3.015143</v>
+        <v>2.876206</v>
       </c>
     </row>
     <row r="198">
@@ -4979,11 +4979,11 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>3.012751</v>
+        <v>2.889313</v>
       </c>
     </row>
     <row r="199">
@@ -5002,11 +5002,11 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>2.955911</v>
+        <v>2.939157</v>
       </c>
     </row>
     <row r="200">
@@ -5025,11 +5025,11 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>3.063218</v>
+        <v>3.015143</v>
       </c>
     </row>
     <row r="201">
@@ -5048,11 +5048,11 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>3.014232</v>
+        <v>3.012751</v>
       </c>
     </row>
     <row r="202">
@@ -5071,11 +5071,11 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>3.077971</v>
+        <v>2.955911</v>
       </c>
     </row>
     <row r="203">
@@ -5094,11 +5094,11 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>3.044699</v>
+        <v>3.063218</v>
       </c>
     </row>
     <row r="204">
@@ -5117,11 +5117,11 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>2.995816</v>
+        <v>3.014232</v>
       </c>
     </row>
     <row r="205">
@@ -5140,11 +5140,11 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>2.948017</v>
+        <v>3.077971</v>
       </c>
     </row>
     <row r="206">
@@ -5163,11 +5163,11 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>2.848562</v>
+        <v>3.044699</v>
       </c>
     </row>
     <row r="207">
@@ -5186,11 +5186,11 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>2.900503</v>
+        <v>2.995816</v>
       </c>
     </row>
     <row r="208">
@@ -5209,11 +5209,11 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>2.881685</v>
+        <v>2.948017</v>
       </c>
     </row>
     <row r="209">
@@ -5232,11 +5232,11 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>2.899034</v>
+        <v>2.848562</v>
       </c>
     </row>
     <row r="210">
@@ -5255,11 +5255,11 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>2.869598</v>
+        <v>2.900503</v>
       </c>
     </row>
     <row r="211">
@@ -5278,11 +5278,11 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>2.942888</v>
+        <v>2.881685</v>
       </c>
     </row>
     <row r="212">
@@ -5301,11 +5301,11 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>2.892125</v>
+        <v>2.899034</v>
       </c>
     </row>
     <row r="213">
@@ -5324,11 +5324,11 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>2.936988</v>
+        <v>2.869598</v>
       </c>
     </row>
     <row r="214">
@@ -5347,11 +5347,11 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>2.946672</v>
+        <v>2.942888</v>
       </c>
     </row>
     <row r="215">
@@ -5370,11 +5370,11 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>2.97218</v>
+        <v>2.892125</v>
       </c>
     </row>
     <row r="216">
@@ -5393,103 +5393,103 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>2.981788</v>
+        <v>2.936988</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>유로존 국채금리 7년</t>
+          <t>유로존 국채금리 5년</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>3.228543</v>
+        <v>2.946672</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>유로존 국채금리 7년</t>
+          <t>유로존 국채금리 5년</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>3.237712</v>
+        <v>2.97218</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>유로존 국채금리 7년</t>
+          <t>유로존 국채금리 5년</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>3.119151</v>
+        <v>2.981788</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>유로존 국채금리 7년</t>
+          <t>유로존 국채금리 5년</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>3.108997</v>
+        <v>2.976278</v>
       </c>
     </row>
     <row r="221">
@@ -5508,11 +5508,11 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>3.118124</v>
+        <v>3.228543</v>
       </c>
     </row>
     <row r="222">
@@ -5531,11 +5531,11 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>3.16475</v>
+        <v>3.237712</v>
       </c>
     </row>
     <row r="223">
@@ -5554,11 +5554,11 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>3.237417</v>
+        <v>3.119151</v>
       </c>
     </row>
     <row r="224">
@@ -5577,11 +5577,11 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>3.240594</v>
+        <v>3.108997</v>
       </c>
     </row>
     <row r="225">
@@ -5600,11 +5600,11 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>3.18189</v>
+        <v>3.118124</v>
       </c>
     </row>
     <row r="226">
@@ -5623,11 +5623,11 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>3.292831</v>
+        <v>3.16475</v>
       </c>
     </row>
     <row r="227">
@@ -5646,11 +5646,11 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>3.250782</v>
+        <v>3.237417</v>
       </c>
     </row>
     <row r="228">
@@ -5669,11 +5669,11 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>3.311581</v>
+        <v>3.240594</v>
       </c>
     </row>
     <row r="229">
@@ -5692,11 +5692,11 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>3.275978</v>
+        <v>3.18189</v>
       </c>
     </row>
     <row r="230">
@@ -5715,11 +5715,11 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>3.226414</v>
+        <v>3.292831</v>
       </c>
     </row>
     <row r="231">
@@ -5738,11 +5738,11 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>3.172951</v>
+        <v>3.250782</v>
       </c>
     </row>
     <row r="232">
@@ -5761,11 +5761,11 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>3.070373</v>
+        <v>3.311581</v>
       </c>
     </row>
     <row r="233">
@@ -5784,11 +5784,11 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>3.121809</v>
+        <v>3.275978</v>
       </c>
     </row>
     <row r="234">
@@ -5807,11 +5807,11 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>3.104055</v>
+        <v>3.226414</v>
       </c>
     </row>
     <row r="235">
@@ -5830,11 +5830,11 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>3.12121</v>
+        <v>3.172951</v>
       </c>
     </row>
     <row r="236">
@@ -5853,11 +5853,11 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>3.091758</v>
+        <v>3.070373</v>
       </c>
     </row>
     <row r="237">
@@ -5876,11 +5876,11 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>3.162397</v>
+        <v>3.121809</v>
       </c>
     </row>
     <row r="238">
@@ -5899,11 +5899,11 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>3.105972</v>
+        <v>3.104055</v>
       </c>
     </row>
     <row r="239">
@@ -5922,11 +5922,11 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>3.150735</v>
+        <v>3.12121</v>
       </c>
     </row>
     <row r="240">
@@ -5945,11 +5945,11 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>3.164004</v>
+        <v>3.091758</v>
       </c>
     </row>
     <row r="241">
@@ -5968,11 +5968,11 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>3.188864</v>
+        <v>3.162397</v>
       </c>
     </row>
     <row r="242">
@@ -5991,126 +5991,126 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>3.200686</v>
+        <v>3.105972</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>3.522383</v>
+        <v>3.150735</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>3.53446</v>
+        <v>3.164004</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>3.419526</v>
+        <v>3.188864</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>3.407866</v>
+        <v>3.200686</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>3.414486</v>
+        <v>3.197992</v>
       </c>
     </row>
     <row r="248">
@@ -6129,11 +6129,11 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>3.459084</v>
+        <v>3.522383</v>
       </c>
     </row>
     <row r="249">
@@ -6152,11 +6152,11 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>3.532267</v>
+        <v>3.53446</v>
       </c>
     </row>
     <row r="250">
@@ -6175,11 +6175,11 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>3.537955</v>
+        <v>3.419526</v>
       </c>
     </row>
     <row r="251">
@@ -6198,11 +6198,11 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>3.477861</v>
+        <v>3.407866</v>
       </c>
     </row>
     <row r="252">
@@ -6221,11 +6221,11 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>3.591227</v>
+        <v>3.414486</v>
       </c>
     </row>
     <row r="253">
@@ -6244,11 +6244,11 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>3.555828</v>
+        <v>3.459084</v>
       </c>
     </row>
     <row r="254">
@@ -6267,11 +6267,11 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>3.614122</v>
+        <v>3.532267</v>
       </c>
     </row>
     <row r="255">
@@ -6290,11 +6290,11 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>3.57531</v>
+        <v>3.537955</v>
       </c>
     </row>
     <row r="256">
@@ -6313,11 +6313,11 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>3.524301</v>
+        <v>3.477861</v>
       </c>
     </row>
     <row r="257">
@@ -6336,11 +6336,11 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>3.465361</v>
+        <v>3.591227</v>
       </c>
     </row>
     <row r="258">
@@ -6359,11 +6359,11 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>3.358616</v>
+        <v>3.555828</v>
       </c>
     </row>
     <row r="259">
@@ -6382,11 +6382,11 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>3.408954</v>
+        <v>3.614122</v>
       </c>
     </row>
     <row r="260">
@@ -6405,11 +6405,11 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>3.392661</v>
+        <v>3.57531</v>
       </c>
     </row>
     <row r="261">
@@ -6428,11 +6428,11 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>3.410886</v>
+        <v>3.524301</v>
       </c>
     </row>
     <row r="262">
@@ -6451,11 +6451,11 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>3.380955</v>
+        <v>3.465361</v>
       </c>
     </row>
     <row r="263">
@@ -6474,11 +6474,11 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>3.450091</v>
+        <v>3.358616</v>
       </c>
     </row>
     <row r="264">
@@ -6497,11 +6497,11 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>3.390251</v>
+        <v>3.408954</v>
       </c>
     </row>
     <row r="265">
@@ -6520,11 +6520,11 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>3.434872</v>
+        <v>3.392661</v>
       </c>
     </row>
     <row r="266">
@@ -6543,11 +6543,11 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>3.451103</v>
+        <v>3.410886</v>
       </c>
     </row>
     <row r="267">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>3.474414</v>
+        <v>3.380955</v>
       </c>
     </row>
     <row r="268">
@@ -6589,11 +6589,149 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>3.450091</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>10</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>3.390251</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>10</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>3.434872</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>10</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>3.451103</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>10</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>20260605</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>3.474414</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>10</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
           <t>20260608</t>
         </is>
       </c>
-      <c r="E268" t="n">
+      <c r="E273" t="n">
         <v>3.487726</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>10</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>3.488064</v>
       </c>
     </row>
   </sheetData>
